--- a/Agentes/Flávia/GEO/Entregas/Segunda Lista de Produtos para GEO 26-08-26_OTIMIZADA.xlsx
+++ b/Agentes/Flávia/GEO/Entregas/Segunda Lista de Produtos para GEO 26-08-26_OTIMIZADA.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom Solteiro Cinza Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom solteiro na cor cinza combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Solteiro&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom solteiro?&lt;/strong&gt;&lt;br /&gt;O edredom mede 1,60 x 2,50 m e foi dimensionado para cama solteiro.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom Solteiro Cinza 1,60 x 2,50 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom solteiro na cor cinza é dimensionado para camas de solteiro, comuns em quartos econômicos e de ocupação individual. O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Solteiro&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas de solteiro, comuns em quartos econômicos e de ocupação individual. A medida informada é 1,60 x 2,50 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>edredom solteiro, edredom cinza, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom solteiro cinza, edredom 1,60x2,50, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom Solteiro Argila Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom solteiro na cor argila combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Solteiro&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom solteiro?&lt;/strong&gt;&lt;br /&gt;O edredom mede 1,60 x 2,50 m e foi dimensionado para cama solteiro.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom Solteiro Argila 1,60 x 2,50 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom solteiro na cor argila é dimensionado para camas de solteiro, comuns em quartos econômicos e de ocupação individual. O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Solteiro&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas de solteiro, comuns em quartos econômicos e de ocupação individual. A medida informada é 1,60 x 2,50 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor argila?&lt;/strong&gt;&lt;br /&gt;O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>edredom solteiro, edredom argila, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom solteiro argila, edredom 1,60x2,50, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom Casal Cinza Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom casal na cor cinza combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,20 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Casal&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom casal?&lt;/strong&gt;&lt;br /&gt;O edredom mede 2,20 x 2,50 m e foi dimensionado para cama casal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom Casal Cinza 2,20 x 2,50 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom casal na cor cinza é dimensionado para camas de casal, padrão em apartamentos de ocupação dupla. O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,20 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Casal&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas de casal, padrão em apartamentos de ocupação dupla. A medida informada é 2,20 x 2,50 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>edredom casal, edredom cinza, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom casal cinza, edredom 2,20x2,50, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom Casal Argila Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom casal na cor argila combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,20 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Casal&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom casal?&lt;/strong&gt;&lt;br /&gt;O edredom mede 2,20 x 2,50 m e foi dimensionado para cama casal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom Casal Argila 2,20 x 2,50 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom casal na cor argila é dimensionado para camas de casal, padrão em apartamentos de ocupação dupla. O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,20 x 2,50 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Casal&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas de casal, padrão em apartamentos de ocupação dupla. A medida informada é 2,20 x 2,50 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor argila?&lt;/strong&gt;&lt;br /&gt;O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>edredom casal, edredom argila, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom casal argila, edredom 2,20x2,50, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom Queen Cinza Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom queen na cor cinza combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,60 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom queen?&lt;/strong&gt;&lt;br /&gt;O edredom mede 2,50 x 2,60 m e foi dimensionado para cama queen.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom Queen Cinza 2,50 x 2,60 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom queen na cor cinza é dimensionado para camas queen, referência em quartos intermediários e superiores. O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,60 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida informada é 2,50 x 2,60 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>edredom queen, edredom cinza, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom queen cinza, edredom 2,50x2,60, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom Queen Argila Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom queen na cor argila combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,60 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom queen?&lt;/strong&gt;&lt;br /&gt;O edredom mede 2,50 x 2,60 m e foi dimensionado para cama queen.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom Queen Argila 2,50 x 2,60 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom queen na cor argila é dimensionado para camas queen, referência em quartos intermediários e superiores. O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,60 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida informada é 2,50 x 2,60 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor argila?&lt;/strong&gt;&lt;br /&gt;O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>edredom queen, edredom argila, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom queen argila, edredom 2,50x2,60, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom King Cinza Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom king na cor cinza combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,80 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom king?&lt;/strong&gt;&lt;br /&gt;O edredom mede 2,50 x 2,80 m e foi dimensionado para cama king.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom King Cinza 2,50 x 2,80 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom king na cor cinza é dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,80 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,50 x 2,80 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>edredom king, edredom cinza, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom king cinza, edredom 2,50x2,80, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Edredom King Argila Dupla Face 150 Fios - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom king na cor argila combina conforto térmico e apresentação padronizada para quartos de hotéis, pousadas, motéis e imóveis de temporada. A tonalidade permite composições neutras e facilita a coordenação com outros itens do enxoval.&lt;/p&gt;&lt;p&gt;As duas faces são confeccionadas em percal 150 fios 100% algodão. A matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, contribuindo para acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,80 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do edredom king?&lt;/strong&gt;&lt;br /&gt;O edredom mede 2,50 x 2,80 m e foi dimensionado para cama king.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto. A escolha depende do clima, da apresentação da cama e da rotina de conservação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada. A medida precisa ser compatível com o colchão e com o caimento planejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O edredom colorido pode ser usado em hotelaria?&lt;/strong&gt;&lt;br /&gt;Sim. Cores padronizadas podem diferenciar categorias de quarto e compor a decoração, desde que a operação mantenha controle de estoque e reposição por modelo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e outros itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Edredom King Argila 2,50 x 2,80 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O edredom king na cor argila é dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;As duas faces são de percal 150 fios 100% algodão e a matelagem mantém distribuída a manta interna de 180 g/m² em 100% poliéster, favorecendo acabamento uniforme e uso recorrente na hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,50 x 2,80 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Cor: Argila&lt;/li&gt;&lt;li&gt;Duas faces em percal 150 fios&lt;/li&gt;&lt;li&gt;Tecido externo: 100% algodão&lt;/li&gt;&lt;li&gt;Enchimento: manta 100% poliéster de 180 g/m²&lt;/li&gt;&lt;li&gt;Acabamento matelado&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição deste edredom?&lt;/strong&gt;&lt;br /&gt;As duas faces são de percal 150 fios 100% algodão, com enchimento em manta 100% poliéster de 180 g/m².&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este edredom é dupla face?&lt;/strong&gt;&lt;br /&gt;Sim. O tecido em percal 150 fios 100% algodão está presente nos dois lados da peça.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este edredom?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,50 x 2,80 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor argila?&lt;/strong&gt;&lt;br /&gt;O argila é um tom terroso que confere sofisticação e acolhimento ao quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre cobertor e edredom?&lt;/strong&gt;&lt;br /&gt;O edredom utiliza enchimento interno e acabamento matelado; o cobertor tem estrutura própria destinada ao aquecimento direto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher edredom para pousada?&lt;/strong&gt;&lt;br /&gt;Considere temperatura da região, dimensões das camas, facilidade de conservação e apresentação desejada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o edredom na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à capacidade dos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar edredom profissional para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece edredons e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>edredom king, edredom argila, edredom hotelaria, percal 150 fios, edredom 100% algodão, edredom para pousada, enxoval profissional, edredom Conamore</t>
+          <t>edredom king argila, edredom 2,50x2,80, edredom hotelaria, edredom percal 150 fios, edredom para pousada, edredom dupla face, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -744,22 +744,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Pezinhos Cinza 50 x 70 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Pezinhos na cor cinza foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 485 g/m², peso de 170 g e composição de 90% algodão e 10% poliéster, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 70 cm&lt;/li&gt;&lt;li&gt;Gramatura: 485 g/m²&lt;/li&gt;&lt;li&gt;Peso: 170 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Desenho de pezinhos em relevo&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Pezinhos?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 485 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 70 cm e pesa 170 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na saída do banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Pezinhos Cinza 50 x 70 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Pezinhos com desenho de pezinhos em relevo cinza é toalha de piso com desenho de pezinhos em relevo, que ajuda a identificá-la e a evitar trocas com a de rosto. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 485 g/m² e peso de 170 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 70 cm&lt;/li&gt;&lt;li&gt;Gramatura: 485 g/m²&lt;/li&gt;&lt;li&gt;Peso: 170 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Desenho de pezinhos em relevo&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 485 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 70 cm e pesa 170 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Pezinhos na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Toalha Piso Pezinhos Cinza 50 x 70 cm | Conamore</t>
+          <t>Toalha Piso Pezinhos Cinza | Conamore</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>toalha de piso, toalha pezinhos, toalha cinza, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de piso pezinhos cinza, toalha 485 g/m², toalha 50x70, toalha de piso hotelaria, pezinhos conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Toalha de piso Pezinhos cinza 50 x 70 cm, 485 g/m² e 90% algodão e 10% poliéster. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de piso Pezinhos cinza 50 x 70 cm, 485 g/m² e 90% algodão e 10% poliéster.</t>
         </is>
       </c>
     </row>
@@ -776,22 +776,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Select Cinza 45 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Select na cor cinza foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 440 g/m², peso de 158 g e composição de 90% algodão e 10% poliéster, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 45 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 158 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Select?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 440 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 45 x 80 cm e pesa 158 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de rosto na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na rotina de higiene do hóspede, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Select Cinza 45 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Select na cor cinza é linha profissional que equilibra maciez e durabilidade, indicada para operações que buscam apresentação premium. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 440 g/m² e peso de 158 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 45 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 158 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 440 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 45 x 80 cm e pesa 158 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Select na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Toalha Rosto Select Cinza 45 x 80 cm | Conamore</t>
+          <t>Toalha Rosto Select Cinza | Conamore</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>toalha de rosto, toalha select, toalha cinza, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de rosto select cinza, toalha 440 g/m², toalha 45x80, toalha de rosto hotelaria, select conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Toalha de rosto Select cinza 45 x 80 cm, 440 g/m² e 90% algodão e 10% poliéster. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de rosto Select cinza 45 x 80 cm, 440 g/m² e 90% algodão e 10% poliéster.</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Select Cinza 80 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Select na cor cinza foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 440 g/m², peso de 490 g e composição de 90% algodão e 10% poliéster, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Select?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 440 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de banho na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso após o banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Select Cinza 80 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Select na cor cinza é linha profissional que equilibra maciez e durabilidade, indicada para operações que buscam apresentação premium. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 440 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 440 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Select na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Toalha Banho Select Cinza 80 x 140 cm | Conamore</t>
+          <t>Toalha Banho Select Cinza | Conamore</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>toalha de banho, toalha select, toalha cinza, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de banho select cinza, toalha 440 g/m², toalha 80x140, toalha de banho hotelaria, select conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toalha de banho Select cinza 80 x 140 cm, 440 g/m² e 90% algodão e 10% poliéster. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de banho Select cinza 80 x 140 cm, 440 g/m² e 90% algodão e 10% poliéster.</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel King Azul 2,40 x 2,70 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O cobertor Flannel king azul oferece toque macio e aveludado para quartos de hotéis, pousadas, motéis e imóveis de temporada. A gramatura de 300 g/m² é indicada para períodos e regiões de clima frio.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster, combina aquecimento, facilidade de lavagem e secagem rápida. A indicação de microfibra é adequada para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 2,40 x 2,70 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, espaço de armazenamento e tamanho das camas. A gramatura de 300 g/m² atende operações que buscam maior aquecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza operacional, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição do Cobertor Flannel?&lt;/strong&gt;&lt;br /&gt;O produto é confeccionado em tecido microflanelado 100% poliéster, com toque macio e aveludado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do Cobertor Flannel King?&lt;/strong&gt;&lt;br /&gt;A medida informada na descrição do produto é 2,40 x 2,70 m. Confira a compatibilidade com a cama e o caimento desejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes e pode melhorar a experiência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e à capacidade dos equipamentos. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel King 2,40 x 2,70 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O Cobertor Flannel king é dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. Indicado para períodos e regiões de clima frio, oferece toque macio e aveludado a quartos de hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster com 300 g/m², combina aquecimento, facilidade de lavagem e secagem rápida. A recomendação de microfibra vale para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 2,40 x 2,70 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, armazenamento e tamanho das camas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é o Cobertor Flannel King?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,40 x 2,70 m; confira a compatibilidade com o colchão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e aos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O cobertor Flannel é mais pesado que a manta de microfibra?&lt;/strong&gt;&lt;br /&gt;Sim. O toque do Flannel é mais macio e a peça tem mais peso que as mantas de microfibra tradicionais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>cobertor king, cobertor flannel, cobertor hotelaria, cobertor 300 g/m², cobertor azul, cobertor para pousada, enxoval profissional, Conamore</t>
+          <t>cobertor king, cobertor flannel azul, cobertor 300 g/m², cobertor para hotel, cobertor microflanelado, cobertor para pousada, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel Queen Azul 2,20 x 2,40 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O cobertor Flannel queen azul oferece toque macio e aveludado para quartos de hotéis, pousadas, motéis e imóveis de temporada. A gramatura de 300 g/m² é indicada para períodos e regiões de clima frio.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster, combina aquecimento, facilidade de lavagem e secagem rápida. A indicação de microfibra é adequada para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 2,20 x 2,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, espaço de armazenamento e tamanho das camas. A gramatura de 300 g/m² atende operações que buscam maior aquecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza operacional, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição do Cobertor Flannel?&lt;/strong&gt;&lt;br /&gt;O produto é confeccionado em tecido microflanelado 100% poliéster, com toque macio e aveludado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do Cobertor Flannel Queen?&lt;/strong&gt;&lt;br /&gt;A medida informada na descrição do produto é 2,20 x 2,40 m. Confira a compatibilidade com a cama e o caimento desejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes e pode melhorar a experiência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e à capacidade dos equipamentos. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel Queen 2,20 x 2,40 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O Cobertor Flannel queen é dimensionado para camas queen, referência em quartos intermediários e superiores. Indicado para períodos e regiões de clima frio, oferece toque macio e aveludado a quartos de hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster com 300 g/m², combina aquecimento, facilidade de lavagem e secagem rápida. A recomendação de microfibra vale para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 2,20 x 2,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, armazenamento e tamanho das camas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é o Cobertor Flannel Queen?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida informada é 2,20 x 2,40 m; confira a compatibilidade com o colchão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e aos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O cobertor Flannel é mais pesado que a manta de microfibra?&lt;/strong&gt;&lt;br /&gt;Sim. O toque do Flannel é mais macio e a peça tem mais peso que as mantas de microfibra tradicionais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>cobertor queen, cobertor flannel, cobertor hotelaria, cobertor 300 g/m², cobertor azul, cobertor para pousada, enxoval profissional, Conamore</t>
+          <t>cobertor queen, cobertor flannel azul, cobertor 300 g/m², cobertor para hotel, cobertor microflanelado, cobertor para pousada, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel Casal Azul 1,80 x 2,20 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O cobertor Flannel casal azul oferece toque macio e aveludado para quartos de hotéis, pousadas, motéis e imóveis de temporada. A gramatura de 300 g/m² é indicada para períodos e regiões de clima frio.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster, combina aquecimento, facilidade de lavagem e secagem rápida. A indicação de microfibra é adequada para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 1,80 x 2,20 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Casal&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, espaço de armazenamento e tamanho das camas. A gramatura de 300 g/m² atende operações que buscam maior aquecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza operacional, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição do Cobertor Flannel?&lt;/strong&gt;&lt;br /&gt;O produto é confeccionado em tecido microflanelado 100% poliéster, com toque macio e aveludado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do Cobertor Flannel Casal?&lt;/strong&gt;&lt;br /&gt;A medida informada na descrição do produto é 1,80 x 2,20 m. Confira a compatibilidade com a cama e o caimento desejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes e pode melhorar a experiência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e à capacidade dos equipamentos. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel Casal 1,80 x 2,20 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O Cobertor Flannel casal é dimensionado para camas de casal, padrão em apartamentos de ocupação dupla. Indicado para períodos e regiões de clima frio, oferece toque macio e aveludado a quartos de hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster com 300 g/m², combina aquecimento, facilidade de lavagem e secagem rápida. A recomendação de microfibra vale para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 1,80 x 2,20 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Casal&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, armazenamento e tamanho das camas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é o Cobertor Flannel Casal?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas de casal, padrão em apartamentos de ocupação dupla. A medida informada é 1,80 x 2,20 m; confira a compatibilidade com o colchão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e aos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O cobertor Flannel é mais pesado que a manta de microfibra?&lt;/strong&gt;&lt;br /&gt;Sim. O toque do Flannel é mais macio e a peça tem mais peso que as mantas de microfibra tradicionais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>cobertor casal, cobertor flannel, cobertor hotelaria, cobertor 300 g/m², cobertor azul, cobertor para pousada, enxoval profissional, Conamore</t>
+          <t>cobertor casal, cobertor flannel azul, cobertor 300 g/m², cobertor para hotel, cobertor microflanelado, cobertor para pousada, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel Solteiro Azul 1,50 x 2,20 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O cobertor Flannel solteiro azul oferece toque macio e aveludado para quartos de hotéis, pousadas, motéis e imóveis de temporada. A gramatura de 300 g/m² é indicada para períodos e regiões de clima frio.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster, combina aquecimento, facilidade de lavagem e secagem rápida. A indicação de microfibra é adequada para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 1,50 x 2,20 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Solteiro&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, espaço de armazenamento e tamanho das camas. A gramatura de 300 g/m² atende operações que buscam maior aquecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza operacional, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição do Cobertor Flannel?&lt;/strong&gt;&lt;br /&gt;O produto é confeccionado em tecido microflanelado 100% poliéster, com toque macio e aveludado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho do Cobertor Flannel Solteiro?&lt;/strong&gt;&lt;br /&gt;A medida informada na descrição do produto é 1,50 x 2,20 m. Confira a compatibilidade com a cama e o caimento desejado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes e pode melhorar a experiência.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e à capacidade dos equipamentos. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Cobertor Flannel Solteiro 1,50 x 2,20 m - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O Cobertor Flannel solteiro é dimensionado para camas de solteiro, comuns em quartos econômicos e de ocupação individual. Indicado para períodos e regiões de clima frio, oferece toque macio e aveludado a quartos de hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;Confeccionado em tecido microflanelado 100% poliéster com 300 g/m², combina aquecimento, facilidade de lavagem e secagem rápida. A recomendação de microfibra vale para cobertores; a Conamore não recomenda lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas informadas na descrição: 1,50 x 2,20 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Solteiro&lt;/li&gt;&lt;li&gt;Cor: azul&lt;/li&gt;&lt;li&gt;Tecido microflanelado (Flannel)&lt;/li&gt;&lt;li&gt;Composição: 100% poliéster&lt;/li&gt;&lt;li&gt;Gramatura: 300 g/m²&lt;/li&gt;&lt;li&gt;Embalagem em PVC com zíper&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual cobertor escolher para hotel?&lt;/strong&gt;&lt;br /&gt;Considere clima, nível de aquecimento, facilidade de lavagem e secagem, armazenamento e tamanho das camas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Cobertor de microfibra é indicado para hospedagem?&lt;/strong&gt;&lt;br /&gt;Sim. Em cobertores, a microfibra oferece leveza, secagem rápida e bom aquecimento. Essa recomendação não se aplica a lençóis de microfibra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura deste cobertor?&lt;/strong&gt;&lt;br /&gt;A gramatura informada é de 300 g/m², indicada para maior aquecimento em dias e noites frias.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é o Cobertor Flannel Solteiro?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas de solteiro, comuns em quartos econômicos e de ocupação individual. A medida informada é 1,50 x 2,20 m; confira a compatibilidade com o colchão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;É necessário oferecer cobertor extra no quarto?&lt;/strong&gt;&lt;br /&gt;Depende do clima e do padrão da hospedagem. Uma opção adicional atende hóspedes com preferências térmicas diferentes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o cobertor na hotelaria?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem ao tecido e aos equipamentos. A etiqueta prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O cobertor Flannel é mais pesado que a manta de microfibra?&lt;/strong&gt;&lt;br /&gt;Sim. O toque do Flannel é mais macio e a peça tem mais peso que as mantas de microfibra tradicionais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar cobertor para hotelaria?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece cobertores e itens de cama para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>cobertor solteiro, cobertor flannel, cobertor hotelaria, cobertor 300 g/m², cobertor azul, cobertor para pousada, enxoval profissional, Conamore</t>
+          <t>cobertor solteiro, cobertor flannel azul, cobertor 300 g/m², cobertor para hotel, cobertor microflanelado, cobertor para pousada, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Kit 250 Sabonetes Capim-limão 10 g - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 250 unidades de sabonetes capim-limão com 10 g cada, em barras individuais. É uma solução para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada que precisam padronizar a reposição de amenities.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. Conforme o cadastro, a linha possui formulação biodegradável, livre de parabenos, não testada em animais e embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 250 unidades&lt;/li&gt;&lt;li&gt;Produto: Sabonetes&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 10 g&lt;/li&gt;&lt;li&gt;Fragrância: Capim-limão&lt;/li&gt;&lt;li&gt;Apresentação: barras individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de sabonete usar em hotel?&lt;/strong&gt;&lt;br /&gt;O tamanho de 10 g atende operações que buscam uma apresentação individual compacta. A escolha deve considerar duração média da estadia, consumo esperado e padrão do estabelecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 250 unidades de sabonetes, cada uma com 10 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a fragrância deste amenity?&lt;/strong&gt;&lt;br /&gt;A fragrância informada é Capim-limão, aplicada à apresentação em barras individuais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades disponibilizadas por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Kit 250 Sabonetes Capim-limão 10 g - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 250 unidades de sabonetes capim-limão com 10 g cada, em barras individuais. A fragrância cítrica de capim-limão é revigorante e de apelo tradicional na hotelaria. É uma solução de reposição para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. A linha possui formulação biodegradável, é livre de parabenos, não testada em animais e tem embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 250 unidades&lt;/li&gt;&lt;li&gt;Produto: Sabonetes&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 10 g&lt;/li&gt;&lt;li&gt;Fragrância: Capim-limão&lt;/li&gt;&lt;li&gt;Apresentação: barras individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de sabonete usar em hotel?&lt;/strong&gt;&lt;br /&gt;O sabonete de 10 g atende operações que buscam apresentação individual compacta. A escolha considera duração média da estadia, consumo esperado e padrão do estabelecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 250 unidades de sabonetes, cada uma com 10 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a fragrância capim-limão?&lt;/strong&gt;&lt;br /&gt;A fragrância cítrica de capim-limão é revigorante e de apelo tradicional na hotelaria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>sabonetes, amenities hotel, capim-limão, kit 250, amenity 10 g, amenities para pousada, higiene para hospedagem, Conamore</t>
+          <t>sabonetes capim-limão, kit 250, amenity 10 g, capim-limão hotelaria, amenities para hotel, amenities para pousada, higiene hospedagem, Conamore</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Kit 250 Sabonetes Herbal 15 g - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 250 unidades de sabonetes herbal com 15 g cada, em barras individuais. É uma solução para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada que precisam padronizar a reposição de amenities.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. Conforme o cadastro, a linha possui formulação biodegradável, livre de parabenos, não testada em animais e embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 250 unidades&lt;/li&gt;&lt;li&gt;Produto: Sabonetes&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 15 g&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: barras individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de sabonete usar em hotel?&lt;/strong&gt;&lt;br /&gt;O tamanho de 15 g atende operações que buscam uma apresentação individual compacta. A escolha deve considerar duração média da estadia, consumo esperado e padrão do estabelecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 250 unidades de sabonetes, cada uma com 15 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a fragrância deste amenity?&lt;/strong&gt;&lt;br /&gt;A fragrância informada é Herbal, aplicada à apresentação em barras individuais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades disponibilizadas por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Kit 250 Sabonetes Herbal 15 g - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 250 unidades de sabonetes herbal com 15 g cada, em barras individuais. A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede. É uma solução de reposição para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. A linha possui formulação biodegradável, é livre de parabenos, não testada em animais e tem embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 250 unidades&lt;/li&gt;&lt;li&gt;Produto: Sabonetes&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 15 g&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: barras individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de sabonete usar em hotel?&lt;/strong&gt;&lt;br /&gt;O sabonete de 15 g atende operações que buscam apresentação individual compacta. A escolha considera duração média da estadia, consumo esperado e padrão do estabelecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 250 unidades de sabonetes, cada uma com 15 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a fragrância herbal?&lt;/strong&gt;&lt;br /&gt;A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sabonetes, amenities hotel, herbal, kit 250, amenity 15 g, amenities para pousada, higiene para hospedagem, Conamore</t>
+          <t>sabonetes herbal, kit 250, amenity 15 g, herbal hotelaria, amenities para hotel, amenities para pousada, higiene hospedagem, Conamore</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Sabonetes Herbal 30 g - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de sabonetes herbal com 30 g cada, em barras individuais. É uma solução para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada que precisam padronizar a reposição de amenities.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. Conforme o cadastro, a linha possui formulação biodegradável, livre de parabenos, não testada em animais e embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Sabonetes&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 30 g&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: barras individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de sabonete usar em hotel?&lt;/strong&gt;&lt;br /&gt;O tamanho de 30 g atende operações que buscam uma apresentação individual compacta. A escolha deve considerar duração média da estadia, consumo esperado e padrão do estabelecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de sabonetes, cada uma com 30 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a fragrância deste amenity?&lt;/strong&gt;&lt;br /&gt;A fragrância informada é Herbal, aplicada à apresentação em barras individuais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades disponibilizadas por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Sabonetes Herbal 30 g - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de sabonetes herbal com 30 g cada, em barras individuais. A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede. É uma solução de reposição para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. A linha possui formulação biodegradável, é livre de parabenos, não testada em animais e tem embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Sabonetes&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 30 g&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: barras individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de sabonete usar em hotel?&lt;/strong&gt;&lt;br /&gt;O sabonete de 30 g atende operações que buscam apresentação individual compacta. A escolha considera duração média da estadia, consumo esperado e padrão do estabelecimento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de sabonetes, cada uma com 30 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a fragrância herbal?&lt;/strong&gt;&lt;br /&gt;A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>sabonetes, amenities hotel, herbal, kit 125, amenity 30 g, amenities para pousada, higiene para hospedagem, Conamore</t>
+          <t>sabonetes herbal, kit 125, amenity 30 g, herbal hotelaria, amenities para hotel, amenities para pousada, higiene hospedagem, Conamore</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Shampoo e Condicionador 2 em 1 Capim-limão 30 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de shampoo e condicionador 2 em 1 capim-limão com 30 ml cada, em sachês individuais. É uma solução para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada que precisam padronizar a reposição de amenities.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. Conforme o cadastro, a linha possui formulação biodegradável, livre de parabenos, não testada em animais e embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Shampoo e Condicionador 2 em 1&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 30 ml&lt;/li&gt;&lt;li&gt;Fragrância: Capim-limão&lt;/li&gt;&lt;li&gt;Apresentação: sachês individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que é shampoo e condicionador 2 em 1 para hotelaria?&lt;/strong&gt;&lt;br /&gt;É um produto que reúne as duas funções em uma apresentação individual de 30 ml, simplificando a composição e a reposição dos amenities.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de shampoo e condicionador 2 em 1, cada uma com 30 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a fragrância deste amenity?&lt;/strong&gt;&lt;br /&gt;A fragrância informada é Capim-limão, aplicada à apresentação em sachês individuais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades disponibilizadas por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Shampoo e Condicionador 2 em 1 Capim-limão 30 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de shampoo e condicionador 2 em 1 capim-limão com 30 ml cada, em sachês individuais. A fragrância cítrica de capim-limão é revigorante e de apelo tradicional na hotelaria. É uma solução de reposição para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. A linha possui formulação biodegradável, é livre de parabenos, não testada em animais e tem embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Shampoo e Condicionador 2 em 1&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 30 ml&lt;/li&gt;&lt;li&gt;Fragrância: Capim-limão&lt;/li&gt;&lt;li&gt;Apresentação: sachês individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que é shampoo e condicionador 2 em 1 para hotelaria?&lt;/strong&gt;&lt;br /&gt;É um produto que reúne as duas funções em uma apresentação individual de 30 ml, simplificando a composição e a reposição dos amenities.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de shampoo e condicionador 2 em 1, cada uma com 30 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a fragrância capim-limão?&lt;/strong&gt;&lt;br /&gt;A fragrância cítrica de capim-limão é revigorante e de apelo tradicional na hotelaria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>shampoo e condicionador 2 em 1, amenities hotel, capim-limão, kit 125, amenity 30 ml, amenities para pousada, higiene para hospedagem, Conamore</t>
+          <t>shampoo e condicionador 2 em 1 capim-limão, kit 125, amenity 30 ml, capim-limão hotelaria, amenities para hotel, amenities para pousada, higiene hospedagem, Conamore</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Shampoo e Condicionador 2 em 1 Capim-limão 35 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de shampoo e condicionador 2 em 1 capim-limão com 35 ml cada, em frascos individuais. É uma solução para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada que precisam padronizar a reposição de amenities.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. Conforme o cadastro, a linha possui formulação biodegradável, livre de parabenos, não testada em animais e embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Shampoo e Condicionador 2 em 1&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 35 ml&lt;/li&gt;&lt;li&gt;Fragrância: Capim-limão&lt;/li&gt;&lt;li&gt;Apresentação: frascos individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que é shampoo e condicionador 2 em 1 para hotelaria?&lt;/strong&gt;&lt;br /&gt;É um produto que reúne as duas funções em uma apresentação individual de 35 ml, simplificando a composição e a reposição dos amenities.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de shampoo e condicionador 2 em 1, cada uma com 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a fragrância deste amenity?&lt;/strong&gt;&lt;br /&gt;A fragrância informada é Capim-limão, aplicada à apresentação em frascos individuais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades disponibilizadas por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Shampoo e Condicionador 2 em 1 Capim-limão 35 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de shampoo e condicionador 2 em 1 capim-limão com 35 ml cada, em frascos individuais. A fragrância cítrica de capim-limão é revigorante e de apelo tradicional na hotelaria. É uma solução de reposição para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. A linha possui formulação biodegradável, é livre de parabenos, não testada em animais e tem embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Shampoo e Condicionador 2 em 1&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 35 ml&lt;/li&gt;&lt;li&gt;Fragrância: Capim-limão&lt;/li&gt;&lt;li&gt;Apresentação: frascos individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que é shampoo e condicionador 2 em 1 para hotelaria?&lt;/strong&gt;&lt;br /&gt;É um produto que reúne as duas funções em uma apresentação individual de 35 ml, simplificando a composição e a reposição dos amenities.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de shampoo e condicionador 2 em 1, cada uma com 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a fragrância capim-limão?&lt;/strong&gt;&lt;br /&gt;A fragrância cítrica de capim-limão é revigorante e de apelo tradicional na hotelaria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>shampoo e condicionador 2 em 1, amenities hotel, capim-limão, kit 125, amenity 35 ml, amenities para pousada, higiene para hospedagem, Conamore</t>
+          <t>shampoo e condicionador 2 em 1 capim-limão, kit 125, amenity 35 ml, capim-limão hotelaria, amenities para hotel, amenities para pousada, higiene hospedagem, Conamore</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Shampoo Herbal 35 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de shampoo herbal com 35 ml cada, em frascos individuais. É uma solução para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada que precisam padronizar a reposição de amenities.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. Conforme o cadastro, a linha possui formulação biodegradável, livre de parabenos, não testada em animais e embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Shampoo&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 35 ml&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: frascos individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de shampoo usar em pousada?&lt;/strong&gt;&lt;br /&gt;O frasco de 35 ml é uma apresentação individual para hospedagem. A quantidade deve ser dimensionada conforme estadia, ocupação e política de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de shampoo, cada uma com 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a fragrância deste amenity?&lt;/strong&gt;&lt;br /&gt;A fragrância informada é Herbal, aplicada à apresentação em frascos individuais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades disponibilizadas por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Shampoo Herbal 35 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de shampoo herbal com 35 ml cada, em frascos individuais. A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede. É uma solução de reposição para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. A linha possui formulação biodegradável, é livre de parabenos, não testada em animais e tem embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Shampoo&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 35 ml&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: frascos individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual tamanho de shampoo usar em pousada?&lt;/strong&gt;&lt;br /&gt;O frasco de 35 ml é uma apresentação individual para hospedagem. A quantidade deve ser dimensionada conforme estadia, ocupação e política de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de shampoo, cada uma com 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a fragrância herbal?&lt;/strong&gt;&lt;br /&gt;A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>shampoo, amenities hotel, herbal, kit 125, amenity 35 ml, amenities para pousada, higiene para hospedagem, Conamore</t>
+          <t>shampoo herbal, kit 125, amenity 35 ml, herbal hotelaria, amenities para hotel, amenities para pousada, higiene hospedagem, Conamore</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Condicionador Herbal 35 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de condicionador herbal com 35 ml cada, em frascos individuais. É uma solução para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada que precisam padronizar a reposição de amenities.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. Conforme o cadastro, a linha possui formulação biodegradável, livre de parabenos, não testada em animais e embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Condicionador&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 35 ml&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: frascos individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que oferecer condicionador em amenities?&lt;/strong&gt;&lt;br /&gt;O condicionador individual complementa o shampoo e amplia a conveniência do hóspede. Este kit usa frascos de 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de condicionador, cada uma com 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a fragrância deste amenity?&lt;/strong&gt;&lt;br /&gt;A fragrância informada é Herbal, aplicada à apresentação em frascos individuais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades disponibilizadas por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Kit 125 Condicionador Herbal 35 ml - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O kit reúne 125 unidades de condicionador herbal com 35 ml cada, em frascos individuais. A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede. É uma solução de reposição para hotéis, pousadas, motéis, clínicas, hospitais e imóveis de temporada.&lt;/p&gt;&lt;p&gt;A apresentação individual oferece conveniência ao hóspede e facilita o controle por hospedagem. A linha possui formulação biodegradável, é livre de parabenos, não testada em animais e tem embalagem reciclável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Conteúdo: 125 unidades&lt;/li&gt;&lt;li&gt;Produto: Condicionador&lt;/li&gt;&lt;li&gt;Volume/peso por unidade: 35 ml&lt;/li&gt;&lt;li&gt;Fragrância: Herbal&lt;/li&gt;&lt;li&gt;Apresentação: frascos individuais&lt;/li&gt;&lt;li&gt;Formulação biodegradável&lt;/li&gt;&lt;li&gt;Livre de parabenos&lt;/li&gt;&lt;li&gt;Não testado em animais&lt;/li&gt;&lt;li&gt;Embalagem reciclável&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;O que são amenities de hotel?&lt;/strong&gt;&lt;br /&gt;São produtos de conveniência oferecidos ao hóspede, como sabonete, shampoo e condicionador, que complementam a experiência de hospedagem.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que oferecer condicionador em amenities?&lt;/strong&gt;&lt;br /&gt;O condicionador individual complementa o shampoo e amplia a conveniência do hóspede. Este kit usa frascos de 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas unidades vêm neste kit?&lt;/strong&gt;&lt;br /&gt;O kit contém 125 unidades de condicionador, cada uma com 35 ml.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a fragrância herbal?&lt;/strong&gt;&lt;br /&gt;A fragrância herbal tem aroma suave e neutro, adequado a diferentes perfis de hóspede.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como calcular a quantidade de amenities necessária?&lt;/strong&gt;&lt;br /&gt;Considere número de apartamentos, ocupação, unidades por hospedagem, consumo médio e intervalo de reposição.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Amenities melhoram a experiência do hóspede?&lt;/strong&gt;&lt;br /&gt;Quando adequados ao posicionamento da hospedagem, transmitem cuidado e oferecem conveniência durante a estadia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Vale a pena oferecer amenities em imóveis de temporada?&lt;/strong&gt;&lt;br /&gt;Pode ser um diferencial de hospitalidade, especialmente em estadias curtas ou para hóspedes que chegam sem itens básicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar amenities para hotel e pousada?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece amenities e outros componentes de enxoval para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>condicionador, amenities hotel, herbal, kit 125, amenity 35 ml, amenities para pousada, higiene para hospedagem, Conamore</t>
+          <t>condicionador herbal, kit 125, amenity 35 ml, herbal hotelaria, amenities para hotel, amenities para pousada, higiene hospedagem, Conamore</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1192,22 +1192,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Branca 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor branca foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 490 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de banho na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso após o banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Branca 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor branca é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toalha Banho Aura Branca 70 x 140 cm | Conamore</t>
+          <t>Toalha Banho Aura Branca | Conamore</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>toalha de banho, toalha aura, toalha branca, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de banho aura branca, toalha 500 g/m², toalha 70x140, toalha de banho hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Toalha de banho Aura branca 70 x 140 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de banho Aura branca 70 x 140 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1224,22 +1224,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor branca foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de rosto na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na rotina de higiene do hóspede, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor branca é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toalha Rosto Aura Branca 50 x 80 cm | Conamore</t>
+          <t>Toalha Rosto Aura Branca | Conamore</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>toalha de rosto, toalha aura, toalha branca, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de rosto aura branca, toalha 500 g/m², toalha 50x80, toalha de rosto hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toalha de rosto Aura branca 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de rosto Aura branca 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1256,22 +1256,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor branca foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na saída do banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor branca é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Toalha Piso Aura Branca 50 x 80 cm | Conamore</t>
+          <t>Toalha Piso Aura Branca | Conamore</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>toalha de piso, toalha aura, toalha branca, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de piso aura branca, toalha 500 g/m², toalha 50x80, toalha de piso hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Toalha de piso Aura branca 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de piso Aura branca 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1288,22 +1288,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Bege 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor bege foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 490 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de banho na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso após o banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Bege 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor bege é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Toalha Banho Aura Bege 70 x 140 cm | Conamore</t>
+          <t>Toalha Banho Aura Bege | Conamore</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>toalha de banho, toalha aura, toalha bege, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de banho aura bege, toalha 500 g/m², toalha 70x140, toalha de banho hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Toalha de banho Aura bege 70 x 140 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de banho Aura bege 70 x 140 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1320,22 +1320,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor bege foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de rosto na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na rotina de higiene do hóspede, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor bege é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Toalha Rosto Aura Bege 50 x 80 cm | Conamore</t>
+          <t>Toalha Rosto Aura Bege | Conamore</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>toalha de rosto, toalha aura, toalha bege, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de rosto aura bege, toalha 500 g/m², toalha 50x80, toalha de rosto hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Toalha de rosto Aura bege 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de rosto Aura bege 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1352,22 +1352,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor bege foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na saída do banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor bege é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Toalha Piso Aura Bege 50 x 80 cm | Conamore</t>
+          <t>Toalha Piso Aura Bege | Conamore</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>toalha de piso, toalha aura, toalha bege, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de piso aura bege, toalha 500 g/m², toalha 50x80, toalha de piso hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Toalha de piso Aura bege 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de piso Aura bege 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1384,22 +1384,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Cinza 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor cinza foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 490 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de banho na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso após o banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Cinza 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor cinza é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Toalha Banho Aura Cinza 70 x 140 cm | Conamore</t>
+          <t>Toalha Banho Aura Cinza | Conamore</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>toalha de banho, toalha aura, toalha cinza, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de banho aura cinza, toalha 500 g/m², toalha 70x140, toalha de banho hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Toalha de banho Aura cinza 70 x 140 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de banho Aura cinza 70 x 140 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1416,22 +1416,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor cinza foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de rosto na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na rotina de higiene do hóspede, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor cinza é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Toalha Rosto Aura Cinza 50 x 80 cm | Conamore</t>
+          <t>Toalha Rosto Aura Cinza | Conamore</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>toalha de rosto, toalha aura, toalha cinza, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de rosto aura cinza, toalha 500 g/m², toalha 50x80, toalha de rosto hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Toalha de rosto Aura cinza 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de rosto Aura cinza 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1448,22 +1448,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor cinza foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na saída do banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor cinza é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Toalha Piso Aura Cinza 50 x 80 cm | Conamore</t>
+          <t>Toalha Piso Aura Cinza | Conamore</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>toalha de piso, toalha aura, toalha cinza, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de piso aura cinza, toalha 500 g/m², toalha 50x80, toalha de piso hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toalha de piso Aura cinza 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de piso Aura cinza 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1480,22 +1480,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Azul 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor azul foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 490 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de banho na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso após o banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Azul 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor azul é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toalha Banho Aura Azul 70 x 140 cm | Conamore</t>
+          <t>Toalha Banho Aura Azul | Conamore</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>toalha de banho, toalha aura, toalha azul, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de banho aura azul, toalha 500 g/m², toalha 70x140, toalha de banho hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Toalha de banho Aura azul 70 x 140 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de banho Aura azul 70 x 140 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1512,22 +1512,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor azul foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de rosto na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na rotina de higiene do hóspede, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor azul é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Toalha Rosto Aura Azul 50 x 80 cm | Conamore</t>
+          <t>Toalha Rosto Aura Azul | Conamore</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>toalha de rosto, toalha aura, toalha azul, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de rosto aura azul, toalha 500 g/m², toalha 50x80, toalha de rosto hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Toalha de rosto Aura azul 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de rosto Aura azul 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1544,22 +1544,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor azul foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na saída do banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor azul é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Toalha Piso Aura Azul 50 x 80 cm | Conamore</t>
+          <t>Toalha Piso Aura Azul | Conamore</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>toalha de piso, toalha aura, toalha azul, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de piso aura azul, toalha 500 g/m², toalha 50x80, toalha de piso hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Toalha de piso Aura azul 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de piso Aura azul 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1576,22 +1576,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Rose 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor rose foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 490 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de banho na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso após o banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Rose 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor rose é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toalha Banho Aura Rose 70 x 140 cm | Conamore</t>
+          <t>Toalha Banho Aura Rose | Conamore</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>toalha de banho, toalha aura, toalha rose, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de banho aura rose, toalha 500 g/m², toalha 70x140, toalha de banho hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Toalha de banho Aura rose 70 x 140 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de banho Aura rose 70 x 140 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1608,22 +1608,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor rose foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de rosto na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na rotina de higiene do hóspede, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor rose é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Toalha Rosto Aura Rose 50 x 80 cm | Conamore</t>
+          <t>Toalha Rosto Aura Rose | Conamore</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>toalha de rosto, toalha aura, toalha rose, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de rosto aura rose, toalha 500 g/m², toalha 50x80, toalha de rosto hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Toalha de rosto Aura rose 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de rosto Aura rose 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor rose foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 500 g/m², peso de 200 g e composição de 100% algodão, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Aura?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 500 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na saída do banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor rose é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Toalha Piso Aura Rose 50 x 80 cm | Conamore</t>
+          <t>Toalha Piso Aura Rose | Conamore</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>toalha de piso, toalha aura, toalha rose, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de piso aura rose, toalha 500 g/m², toalha 50x80, toalha de piso hotelaria, aura conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Toalha de piso Aura rose 50 x 80 cm, 500 g/m² e 100% algodão. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de piso Aura rose 50 x 80 cm, 500 g/m² e 100% algodão.</t>
         </is>
       </c>
     </row>
@@ -1672,22 +1672,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Imperial Branca 80 x 150 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Imperial na cor branca foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 600 g/m², peso de 720 g e composição de 90% algodão e 10% poliéster, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 150 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 720 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Imperial?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 600 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 150 cm e pesa 720 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de banho na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso após o banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Imperial Branca 80 x 150 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Imperial na cor branca é linha de fio retorcido e alta gramatura, pensada para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 600 g/m² e peso de 720 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 150 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 720 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 600 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 150 cm e pesa 720 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Toalha Banho Imperial Branca 80 x 150 cm | Conamore</t>
+          <t>Toalha Banho Imperial Branca | Conamore</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>toalha de banho, toalha imperial, toalha branca, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de banho imperial branca, toalha 600 g/m², toalha 80x150, toalha de banho hotelaria, imperial conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Toalha de banho Imperial branca 80 x 150 cm, 600 g/m² e 90% algodão e 10% poliéster. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de banho Imperial branca 80 x 150 cm, 600 g/m² e 90% algodão e 10% poliéster.</t>
         </is>
       </c>
     </row>
@@ -1704,22 +1704,22 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Imperial na cor branca foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 600 g/m², peso de 240 g e composição de 90% algodão e 10% poliéster, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 240 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Imperial?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 600 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 240 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de rosto na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na rotina de higiene do hóspede, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Imperial na cor branca é linha de fio retorcido e alta gramatura, pensada para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 600 g/m² e peso de 240 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 240 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 600 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 240 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Toalha Rosto Imperial Branca 50 x 80 cm | Conamore</t>
+          <t>Toalha Rosto Imperial Branca | Conamore</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>toalha de rosto, toalha imperial, toalha branca, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de rosto imperial branca, toalha 600 g/m², toalha 50x80, toalha de rosto hotelaria, imperial conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Toalha de rosto Imperial branca 50 x 80 cm, 600 g/m² e 90% algodão e 10% poliéster. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de rosto Imperial branca 50 x 80 cm, 600 g/m² e 90% algodão e 10% poliéster.</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1736,22 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Imperial na cor branca foi desenvolvida para compor enxovais de hotéis, pousadas, motéis, clínicas e imóveis de temporada. A construção combina absorção, toque confortável e padronização para operações de hospedagem.&lt;/p&gt;&lt;p&gt;Com gramatura de 700 g/m², peso de 280 g e composição de 90% algodão e 10% poliéster, a peça reúne características relevantes para uso recorrente. Para a conservação, o processo de lavanderia deve sempre respeitar a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 700 g/m²&lt;/li&gt;&lt;li&gt;Peso: 280 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura da toalha Imperial?&lt;/strong&gt;&lt;br /&gt;Esta toalha tem gramatura de 700 g/m², característica que contribui para volume, absorção e percepção de conforto. A gramatura deve ser avaliada junto com composição, peso e rotina de lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação deve orientar a escolha e o processo de conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 280 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso na hospedagem?&lt;/strong&gt;&lt;br /&gt;É indicada para uso na saída do banho, ajudando a compor um enxoval padronizado para hotéis, pousadas, motéis e imóveis de temporada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a oferecer mais volume e absorção, mas também influencia peso, lavagem e secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga sempre as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece sobre recomendações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como saber quando substituir uma toalha de hotel?&lt;/strong&gt;&lt;br /&gt;Perda relevante de absorção ou maciez, manchas permanentes, desfiados e bordas comprometidas indicam que a peça deve ser avaliada para retirada de circulação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Imperial na cor branca é linha de fio retorcido e alta gramatura, pensada para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 700 g/m² e peso de 280 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 700 g/m²&lt;/li&gt;&lt;li&gt;Peso: 280 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 700 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 280 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Toalha Piso Imperial Branca 50 x 80 cm | Conamore</t>
+          <t>Toalha Piso Imperial Branca | Conamore</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>toalha de piso, toalha imperial, toalha branca, toalha para hotel, toalha para pousada, enxoval de banho, toalha profissional, Conamore</t>
+          <t>toalha de piso imperial branca, toalha 700 g/m², toalha 50x80, toalha de piso hotelaria, imperial conamore, toalha para hotel</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Toalha de piso Imperial branca 50 x 80 cm, 700 g/m² e 90% algodão e 10% poliéster. Para hotéis, pousadas e imóveis de temporada.</t>
+          <t>Toalha de piso Imperial branca 50 x 80 cm, 700 g/m² e 90% algodão e 10% poliéster.</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Verde - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king na cor verde é confeccionado em percal 150 fios 100% algodão. O tecido oferece toque natural e pode compor quartos residenciais e enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;O elástico ajuda a manter a peça ajustada ao colchão. A medida de 2,00 x 2,00 x 0,25 m, incluindo bolsão de 25 cm, deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,25 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 25 cm&lt;/li&gt;&lt;li&gt;Cor: Verde&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades. A conservação deve seguir a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,25 m, a terceira medida corresponde à profundidade do bolsão: 25 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este lençol serve em cama king?&lt;/strong&gt;&lt;br /&gt;Sim, o cadastro indica tamanho king com medida de 2,00 x 2,00 x 0,25 m. Confirme as dimensões do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o lençol 100% algodão?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à composição. A etiqueta do produto prevalece sobre orientações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Verde - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king na cor verde é confeccionado em percal 150 fios 100% algodão. O verde transmite frescor e diferencia o enxoval de forma discreta. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida de 2,00 x 2,00 x 0,25 m inclui bolsão de 25 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,25 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 25 cm&lt;/li&gt;&lt;li&gt;Cor: Verde&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,00 x 2,00 x 0,25 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor verde?&lt;/strong&gt;&lt;br /&gt;O verde transmite frescor e diferencia o enxoval de forma discreta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,25 m, a terceira medida corresponde à profundidade do bolsão: 25 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>lençol king, lençol Amore, lençol verde, lençol 150 fios, lençol 100% algodão, lençol com elástico, enxoval de cama, Conamore</t>
+          <t>lençol king verde, lençol Amore, lençol 150 fios, lençol 100% algodão, lençol com elástico, lençol avulso, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Lençol king Amore verde com elástico, percal 150 fios 100% algodão e bolsão de 25 cm. Para casas e imóveis de temporada.</t>
+          <t>Lençol king Amore verde com elástico, percal 150 fios 100% algodão e bolsão de 25 cm.</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Lençol Queen com Elástico Amore 150 Fios Lilás - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore queen na cor lilás é confeccionado em percal 150 fios 100% algodão. O tecido oferece toque natural e pode compor quartos residenciais e enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;O elástico ajuda a manter a peça ajustada ao colchão. A medida de 1,60 x 2,00 x 0,40 m, incluindo bolsão de 40 cm, deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Lilás&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades. A conservação deve seguir a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 1,60 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este lençol serve em cama queen?&lt;/strong&gt;&lt;br /&gt;Sim, o cadastro indica tamanho queen com medida de 1,60 x 2,00 x 0,40 m. Confirme as dimensões do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o lençol 100% algodão?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à composição. A etiqueta do produto prevalece sobre orientações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Lençol Queen com Elástico Amore 150 Fios Lilás - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore queen na cor lilás é confeccionado em percal 150 fios 100% algodão. O lilás é um tom delicado que suaviza a composição da cama. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida de 1,60 x 2,00 x 0,40 m inclui bolsão de 40 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Lilás&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida informada é 1,60 x 2,00 x 0,40 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor lilás?&lt;/strong&gt;&lt;br /&gt;O lilás é um tom delicado que suaviza a composição da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 1,60 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>lençol queen, lençol Amore, lençol lilás, lençol 150 fios, lençol 100% algodão, lençol com elástico, enxoval de cama, Conamore</t>
+          <t>lençol queen lilás, lençol Amore, lençol 150 fios, lençol 100% algodão, lençol com elástico, lençol avulso, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Lençol queen Amore lilás com elástico, percal 150 fios 100% algodão e bolsão de 40 cm. Para casas e imóveis de temporada.</t>
+          <t>Lençol queen Amore lilás com elástico, percal 150 fios 100% algodão e bolsão de 40 cm.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Branco - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king na cor branco é confeccionado em percal 150 fios 100% algodão. O tecido oferece toque natural e pode compor quartos residenciais e enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;O elástico ajuda a manter a peça ajustada ao colchão. A medida de 2,00 x 2,00 x 0,40 m, incluindo bolsão de 40 cm, deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Branco&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades. A conservação deve seguir a etiqueta do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Este lençol serve em cama king?&lt;/strong&gt;&lt;br /&gt;Sim, o cadastro indica tamanho king com medida de 2,00 x 2,00 x 0,40 m. Confirme as dimensões do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar o lençol 100% algodão?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste lavagem e secagem à composição. A etiqueta do produto prevalece sobre orientações gerais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Branco - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king na cor branco é confeccionado em percal 150 fios 100% algodão. O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida de 2,00 x 2,00 x 0,40 m inclui bolsão de 40 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Branco&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,00 x 2,00 x 0,40 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor branco?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>lençol king, lençol Amore, lençol branco, lençol 150 fios, lençol 100% algodão, lençol com elástico, enxoval de cama, Conamore</t>
+          <t>lençol king branco, lençol Amore, lençol 150 fios, lençol 100% algodão, lençol com elástico, lençol avulso, enxoval de cama, Conamore</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Lençol king Amore branco com elástico, percal 150 fios 100% algodão e bolsão de 40 cm. Para casas e imóveis de temporada.</t>
+          <t>Lençol king Amore branco com elástico, percal 150 fios 100% algodão e bolsão de 40 cm.</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>O name informa 485 g/m² e 170 g; o início da description original informa 450 g/m² e 157 g, enquanto o corpo volta a informar 485 g/m². A versão otimizada mantém os dados do name (485 g/m² e 170 g). Validar antes da importação.</t>
+          <t>O name informa 485 g/m² e 170 g; o início da description original informa 450 g/m² e 157 g, e o corpo volta a informar 485 g/m². A versão otimizada mantém os dados do name (485 g/m² e 170 g). Validar antes da importação.</t>
         </is>
       </c>
     </row>

--- a/Agentes/Flávia/GEO/Entregas/Segunda Lista de Produtos para GEO 26-08-26_OTIMIZADA.xlsx
+++ b/Agentes/Flávia/GEO/Entregas/Segunda Lista de Produtos para GEO 26-08-26_OTIMIZADA.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Pezinhos Cinza 50 x 70 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Pezinhos com desenho de pezinhos em relevo cinza é toalha de piso com desenho de pezinhos em relevo, que ajuda a identificá-la e a evitar trocas com a de rosto. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 485 g/m² e peso de 170 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 70 cm&lt;/li&gt;&lt;li&gt;Gramatura: 485 g/m²&lt;/li&gt;&lt;li&gt;Peso: 170 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Desenho de pezinhos em relevo&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 485 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 70 cm e pesa 170 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Pezinhos na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Pezinhos Cinza 50 x 70 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Pezinhos na cor cinza tem desenho de pezinhos em relevo, que ajuda a identificá-la no enxoval e a evitar trocas com a toalha de rosto. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 485 g/m² e peso de 170 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 70 cm&lt;/li&gt;&lt;li&gt;Gramatura: 485 g/m²&lt;/li&gt;&lt;li&gt;Peso: 170 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Desenho de pezinhos em relevo&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 485 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 70 cm e pesa 170 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Pezinhos na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Select Cinza 45 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Select na cor cinza é linha profissional que equilibra maciez e durabilidade, indicada para operações que buscam apresentação premium. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 440 g/m² e peso de 158 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 45 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 158 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 440 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 45 x 80 cm e pesa 158 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Select na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Select Cinza 45 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Select na cor cinza faz parte da linha Select, que equilibra maciez e durabilidade para uma apresentação premium. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 440 g/m² e peso de 158 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 45 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 158 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 440 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 45 x 80 cm e pesa 158 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Select na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Select Cinza 80 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Select na cor cinza é linha profissional que equilibra maciez e durabilidade, indicada para operações que buscam apresentação premium. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 440 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 440 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Select na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Select Cinza 80 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Select na cor cinza faz parte da linha Select, que equilibra maciez e durabilidade para uma apresentação premium. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 440 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 440 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Costura dupla nas laterais&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 440 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Select na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Branca 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor branca é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Branca 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor branca faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor branca é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor branca faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor branca é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor branca faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Bege 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor bege é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Bege 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor bege faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor bege é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor bege faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor bege é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Bege 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor bege faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Bege&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor bege?&lt;/strong&gt;&lt;br /&gt;O bege é um tom quente que suaviza o ambiente e combina com decorações claras.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Cinza 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor cinza é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Cinza 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor cinza faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor cinza é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor cinza faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor cinza é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Cinza 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor cinza faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Cinza&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor cinza?&lt;/strong&gt;&lt;br /&gt;O cinza é um tom neutro que disfarça o uso recorrente e harmoniza com decorações contemporâneas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Azul 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor azul é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Azul 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor azul faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor azul é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor azul faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor azul é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Azul 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor azul faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Azul&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor azul?&lt;/strong&gt;&lt;br /&gt;O azul permite diferenciar categorias de quarto sem perder sobriedade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Rose 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor rose é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Aura Rose 70 x 140 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Aura na cor rose faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 490 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 70 x 140 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 490 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 70 x 140 cm e pesa 490 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor rose é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Aura na cor rose faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor rose é linha em 100% algodão com fio cardado 24/2, desenvolvida para unir o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Aura Rose 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Aura na cor rose faz parte da linha Aura, 100% algodão com fio cardado 24/2, que une o padrão hoteleiro ao conforto do uso residencial. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor. A peça tem gramatura de 500 g/m² e peso de 200 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 500 g/m²&lt;/li&gt;&lt;li&gt;Peso: 200 g&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Cor: Rose&lt;/li&gt;&lt;li&gt;Fio cardado 24/2&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 500 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 100% algodão. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 200 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Aura na cor rose?&lt;/strong&gt;&lt;br /&gt;O rosé adiciona personalidade ao enxoval mantendo um aspecto acolhedor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Imperial Branca 80 x 150 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Imperial na cor branca é linha de fio retorcido e alta gramatura, pensada para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 600 g/m² e peso de 720 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 150 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 720 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 600 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 150 cm e pesa 720 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Banho Imperial Branca 80 x 150 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de banho Imperial na cor branca faz parte da linha Imperial, de fio retorcido e alta gramatura para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada no pós-banho, quando absorção e volume são mais percebidos pelo hóspede.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 600 g/m² e peso de 720 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 80 x 150 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 720 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 600 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de banho?&lt;/strong&gt;&lt;br /&gt;A peça mede 80 x 150 cm e pesa 720 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de banho e banhão?&lt;/strong&gt;&lt;br /&gt;O banhão é a toalha de banho em tamanho extra grande. A toalha de banho padrão atende o uso diário; o banhão é opção para hotéis premium e SPAs.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Toalha de banho com maior gramatura é sempre melhor?&lt;/strong&gt;&lt;br /&gt;Não. Maior gramatura tende a dar mais volume e absorção, mas também influencia peso e tempo de secagem. A escolha deve considerar a experiência desejada e a operação da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Imperial na cor branca é linha de fio retorcido e alta gramatura, pensada para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 600 g/m² e peso de 240 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 240 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 600 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 240 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Rosto Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de rosto Imperial na cor branca faz parte da linha Imperial, de fio retorcido e alta gramatura para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada na rotina de higiene, compondo o kit padrão por banheiro.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 600 g/m² e peso de 240 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 600 g/m²&lt;/li&gt;&lt;li&gt;Peso: 240 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 600 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de rosto?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 240 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hotel deve oferecer toalha de rosto?&lt;/strong&gt;&lt;br /&gt;É prática comum e aumenta a comodidade do hóspede. A composição do kit depende da categoria e da proposta de serviço.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Quantas toalhas devo ter por banheiro?&lt;/strong&gt;&lt;br /&gt;O kit comum é 2 toalhas de banho, 1 de rosto e 1 de piso por banheiro. O número ideal varia com ocupação e velocidade da lavanderia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Imperial na cor branca é linha de fio retorcido e alta gramatura, pensada para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 700 g/m² e peso de 280 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 700 g/m²&lt;/li&gt;&lt;li&gt;Peso: 280 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 700 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 280 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Toalha de Piso Imperial Branca 50 x 80 cm - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;A toalha de piso Imperial na cor branca faz parte da linha Imperial, de fio retorcido e alta gramatura para uso intenso em hotéis, pousadas, motéis e clínicas. No quarto, ela é usada na saída do banho, ajudando a manter o piso mais seco.&lt;/p&gt;&lt;p&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. A peça tem gramatura de 700 g/m² e peso de 280 g.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 50 x 80 cm&lt;/li&gt;&lt;li&gt;Gramatura: 700 g/m²&lt;/li&gt;&lt;li&gt;Peso: 280 g&lt;/li&gt;&lt;li&gt;Composição: 90% algodão e 10% poliéster&lt;/li&gt;&lt;li&gt;Cor: Branca&lt;/li&gt;&lt;li&gt;Fio retorcido&lt;/li&gt;&lt;li&gt;Indicada para lavagem industrial&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Qual é a gramatura desta toalha?&lt;/strong&gt;&lt;br /&gt;A gramatura é de 700 g/m², característica que contribui para volume, absorção e percepção de conforto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é a composição desta toalha?&lt;/strong&gt;&lt;br /&gt;A composição informada é 90% algodão e 10% poliéster. Essa informação orienta a escolha e a conservação do enxoval.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual é o tamanho da toalha de piso?&lt;/strong&gt;&lt;br /&gt;A peça mede 50 x 80 cm e pesa 280 g, conforme o cadastro do produto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para que serve a toalha de piso no hotel?&lt;/strong&gt;&lt;br /&gt;É usada na saída do banho, proporcionando conforto e mantendo o piso mais seco. O desenho ou a padronização ajudam a diferenciá-la da toalha de rosto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qual a diferença entre toalha de piso e de rosto?&lt;/strong&gt;&lt;br /&gt;A de piso é usada no chão, na saída do banho; a de rosto, na higiene das mãos e do rosto. Diferenciá-las evita trocas no dia a dia da governança.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a toalha Imperial na cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como conservar toalhas de hotel?&lt;/strong&gt;&lt;br /&gt;Siga as instruções da etiqueta e ajuste dosagens, lavagem e secagem à composição da peça. A etiqueta do produto prevalece.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar toalhas profissionais para hotel?&lt;/strong&gt;&lt;br /&gt;A Conamore é especializada em enxoval para hotelaria e oferece toalhas para hotéis, pousadas, motéis, clínicas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Verde - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king na cor verde é confeccionado em percal 150 fios 100% algodão. O verde transmite frescor e diferencia o enxoval de forma discreta. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida de 2,00 x 2,00 x 0,25 m inclui bolsão de 25 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,25 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 25 cm&lt;/li&gt;&lt;li&gt;Cor: Verde&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,00 x 2,00 x 0,25 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor verde?&lt;/strong&gt;&lt;br /&gt;O verde transmite frescor e diferencia o enxoval de forma discreta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,25 m, a terceira medida corresponde à profundidade do bolsão: 25 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Verde - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king verde é confeccionado em percal 150 fios 100% algodão. O verde transmite frescor e diferencia o enxoval de forma discreta. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida de 2,00 x 2,00 x 0,25 m inclui bolsão de 25 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,25 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 25 cm&lt;/li&gt;&lt;li&gt;Cor: Verde&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,00 x 2,00 x 0,25 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor verde?&lt;/strong&gt;&lt;br /&gt;O verde transmite frescor e diferencia o enxoval de forma discreta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,25 m, a terceira medida corresponde à profundidade do bolsão: 25 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Lençol Queen com Elástico Amore 150 Fios Lilás - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore queen na cor lilás é confeccionado em percal 150 fios 100% algodão. O lilás é um tom delicado que suaviza a composição da cama. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida de 1,60 x 2,00 x 0,40 m inclui bolsão de 40 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Lilás&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida informada é 1,60 x 2,00 x 0,40 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor lilás?&lt;/strong&gt;&lt;br /&gt;O lilás é um tom delicado que suaviza a composição da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 1,60 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Lençol Queen com Elástico Amore 150 Fios Lilás - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore queen lilás é confeccionado em percal 150 fios 100% algodão. O lilás é um tom delicado que suaviza a composição da cama. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida de 1,60 x 2,00 x 0,40 m inclui bolsão de 40 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 1,60 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: Queen&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Lilás&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas queen, referência em quartos intermediários e superiores. A medida informada é 1,60 x 2,00 x 0,40 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor lilás?&lt;/strong&gt;&lt;br /&gt;O lilás é um tom delicado que suaviza a composição da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 1,60 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Branco - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king na cor branco é confeccionado em percal 150 fios 100% algodão. O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida de 2,00 x 2,00 x 0,40 m inclui bolsão de 40 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Branco&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,00 x 2,00 x 0,40 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor branco?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Lençol King com Elástico Amore 150 Fios Branco - Conamore&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;O lençol avulso Amore king branco é confeccionado em percal 150 fios 100% algodão. O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto. Atende o uso residencial e compõe enxovais de imóveis de temporada que priorizam conforto.&lt;/p&gt;&lt;p&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida de 2,00 x 2,00 x 0,40 m inclui bolsão de 40 cm, que deve ser conferida com largura, comprimento e altura do colchão antes da compra.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Características:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Medidas: 2,00 x 2,00 x 0,40 m&lt;/li&gt;&lt;li&gt;Tamanho de cama: King&lt;/li&gt;&lt;li&gt;Profundidade do bolsão: 40 cm&lt;/li&gt;&lt;li&gt;Cor: Branco&lt;/li&gt;&lt;li&gt;Percal 150 fios&lt;/li&gt;&lt;li&gt;Composição: 100% algodão&lt;/li&gt;&lt;li&gt;Peça avulsa com elástico&lt;/li&gt;&lt;/ul&gt;&lt;h3&gt;Perguntas frequentes&lt;/h3&gt;&lt;p&gt;&lt;strong&gt;Lençol 100% algodão oferece quais características?&lt;/strong&gt;&lt;br /&gt;O algodão proporciona toque natural e é valorizado quando conforto e percepção de qualidade são prioridades.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa percal?&lt;/strong&gt;&lt;br /&gt;Percal é uma construção de tecido de trama firme e toque seco e fresco. Contagem de fios, composição e acabamento devem ser avaliados em conjunto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Como escolher o tamanho correto do lençol com elástico?&lt;/strong&gt;&lt;br /&gt;Meça largura, comprimento e altura do colchão. A profundidade do bolsão é essencial para que o lençol vista corretamente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Para qual tipo de cama é este lençol?&lt;/strong&gt;&lt;br /&gt;É dimensionado para camas king, presentes em suítes e apartamentos de alto padrão. A medida informada é 2,00 x 2,00 x 0,40 m.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que escolher a cor branca?&lt;/strong&gt;&lt;br /&gt;O branco transmite limpeza, facilita a inspeção do enxoval e se integra a qualquer padronização de quarto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O que significa a terceira medida do lençol?&lt;/strong&gt;&lt;br /&gt;Na medida 2,00 x 2,00 x 0,40 m, a terceira medida corresponde à profundidade do bolsão: 40 cm.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Lençol com elástico substitui o lençol de cima?&lt;/strong&gt;&lt;br /&gt;Não. O lençol com elástico fixa sobre o colchão; o lençol plano ou de cima cumpre outra função na montagem da cama.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Onde comprar lençol de algodão para hospedagem?&lt;/strong&gt;&lt;br /&gt;A Conamore oferece lençóis e itens de cama para residências, hotéis, pousadas e imóveis de temporada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
